--- a/results/Int Task Remove ACC -0.6/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6658227659193436</v>
+        <v>0.6678673153509632</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6672209762101714</v>
+        <v>0.6669118420416784</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6672209762101714</v>
+        <v>0.6627061960436511</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6566375725221653</v>
+        <v>0.6433803359400095</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6531432904383024</v>
+        <v>0.6336333711400868</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6531432904383024</v>
+        <v>0.6291836157469393</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6570312744287059</v>
+        <v>0.6380131271870354</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6579597429140763</v>
+        <v>0.6243291433217071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6603379440516901</v>
+        <v>0.6128147838619172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6574740114102487</v>
+        <v>0.5987616156275495</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6549327153492577</v>
+        <v>0.5989652177867983</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6591138438097837</v>
+        <v>0.6098662834824284</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6591138438097837</v>
+        <v>0.6157742993669502</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6581093354254965</v>
+        <v>0.6046696315120712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6573219316124155</v>
+        <v>0.6079627987230982</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6575795434194929</v>
+        <v>0.5881782119395433</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.657261881411869</v>
+        <v>0.5935809533555626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6483563300728562</v>
+        <v>0.5746512824448746</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6525655293371879</v>
+        <v>0.5715997373425548</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6555005273047196</v>
+        <v>0.593722018027852</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6732270622446979</v>
+        <v>0.5823242057028503</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.666211493253058</v>
+        <v>0.5816778665620586</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6641534414094812</v>
+        <v>0.5856038705019202</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6622904638860225</v>
+        <v>0.5743435695829033</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6599552572706935</v>
+        <v>0.5745901662644369</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6734025936001411</v>
+        <v>0.5697221914272476</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6759904374497213</v>
+        <v>0.5763060385628885</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6794712171216268</v>
+        <v>0.5922467018582162</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6798833960129509</v>
+        <v>0.5858799592937812</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6813196262532371</v>
+        <v>0.5982197425161104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6767458618660618</v>
+        <v>0.5988550665313582</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6897294969427696</v>
+        <v>0.6124960558744019</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.695577462626745</v>
+        <v>0.6099313082558011</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6966985181458203</v>
+        <v>0.6099313082558011</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.694097171884283</v>
+        <v>0.6035290330283209</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.715033372277132</v>
+        <v>0.6030457888109065</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7085991176529113</v>
+        <v>0.5913573193021954</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.718276083106635</v>
+        <v>0.5950171835958487</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6575720815602535</v>
+        <v>0.5904828604646535</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6646587158779838</v>
+        <v>0.6016010307314896</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6961648175468818</v>
+        <v>0.6021553402749944</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6886635170514144</v>
+        <v>0.5723540957790039</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.68917127880633</v>
+        <v>0.5736737788845018</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7266664108314927</v>
+        <v>0.5748683870160807</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.72294400905088</v>
+        <v>0.5649362970416926</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7365604808564226</v>
+        <v>0.5649362970416926</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7211606246926425</v>
+        <v>0.5522923542236966</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7436400086415436</v>
+        <v>0.5532453402465682</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7436400086415436</v>
+        <v>0.5198382411047532</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7371076838673182</v>
+        <v>0.5472577311968254</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7311321559230106</v>
+        <v>0.56671968139993</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7422723564409348</v>
+        <v>0.5841591124225033</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7549923391578475</v>
+        <v>0.604866127138711</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7528312425914399</v>
+        <v>0.5780020125700349</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7533144868088542</v>
+        <v>0.5763071045427799</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7301027746745918</v>
+        <v>0.5965589458453788</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7212032638882966</v>
+        <v>0.5965589458453788</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7160886923695737</v>
+        <v>0.5965589458453788</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7119750759688336</v>
+        <v>0.6036064942337594</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6631468010654114</v>
+        <v>0.5908374764418444</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6601602807364642</v>
+        <v>0.5944348032485381</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6318503421084798</v>
+        <v>0.5953387541964075</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6474637495771614</v>
+        <v>0.5552102965129666</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6166395197121002</v>
+        <v>0.5535324441639733</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6362720266978217</v>
+        <v>0.5428200569091132</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6596208949114384</v>
+        <v>0.5265212243702901</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6640425795007803</v>
+        <v>0.5270805084866212</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.664449783819278</v>
+        <v>0.5421111802813618</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6816525673059703</v>
+        <v>0.5389469966371887</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6816525673059703</v>
+        <v>0.5360560591718331</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6577884754781986</v>
+        <v>0.5290429774666064</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6370782628223168</v>
+        <v>0.5265151838175725</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6078938653567906</v>
+        <v>0.541712503801995</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5983629391481826</v>
+        <v>0.5185906893052369</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6171909866425613</v>
+        <v>0.5143690536088394</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6527737507426327</v>
+        <v>0.517053901628533</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6511339183430978</v>
+        <v>0.5347608936038364</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6463529985303691</v>
+        <v>0.5265912237164891</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6412323864589285</v>
+        <v>0.5246337293093304</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6357106106217079</v>
+        <v>0.514242912655029</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5904668707662832</v>
+        <v>0.5193340326161421</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6123390015037423</v>
+        <v>0.5199313366819315</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6117036774884945</v>
+        <v>0.5188642908106849</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5952147452023798</v>
+        <v>0.5268928960257427</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5955754017322884</v>
+        <v>0.5189097726193826</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5063916154285666</v>
+        <v>0.5270229455724881</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5063916154285666</v>
+        <v>0.5321851308596914</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5156898026942287</v>
+        <v>0.5203598605982563</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4934424470350125</v>
+        <v>0.5025349001816429</v>
       </c>
     </row>
   </sheetData>
